--- a/docs/CMVFOperatingRoomStatus.xlsx
+++ b/docs/CMVFOperatingRoomStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOperatingRoomStatus.xlsx
+++ b/docs/CMVFOperatingRoomStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFOperatingRoomStatus.xlsx
+++ b/docs/CMVFOperatingRoomStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t/>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-status</t>
+    <t>http://hl7.org/fhir/location-status</t>
   </si>
   <si>
     <t>1</t>

--- a/docs/CMVFOperatingRoomStatus.xlsx
+++ b/docs/CMVFOperatingRoomStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
